--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>115643707</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>115643707</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>115643707</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1863,6 +1863,1078 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125807652</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>492587</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6939939</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125807651</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>492607</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6939885</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125807658</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>492561</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6939925</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125807666</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>492390</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6939993</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125807655</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>492567</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6939911</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125807660</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79053</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>492533</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6940061</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125807653</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>492583</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6939941</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125807659</v>
+      </c>
+      <c r="B20" t="n">
+        <v>75066</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>492549</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6939896</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125807656</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>492565</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6939923</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125807654</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>492577</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6939946</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125807657</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>492561</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6939925</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2935,6 +2935,434 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125777398</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98349</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>492382</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6939966</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125777308</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>492485</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6940017</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125777352</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>492414</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6939990</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125777424</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>492372</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6939969</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>125777308</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>91921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>125777352</v>
       </c>
       <c r="B26" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125777424</v>
       </c>
       <c r="B27" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>125807652</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>125807658</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>125807660</v>
       </c>
       <c r="B18" t="n">
-        <v>79053</v>
+        <v>79054</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>125807653</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>125807659</v>
       </c>
       <c r="B20" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>125807656</v>
       </c>
       <c r="B21" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>125807654</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>125807657</v>
       </c>
       <c r="B23" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>125777308</v>
       </c>
       <c r="B25" t="n">
-        <v>91921</v>
+        <v>91922</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>125777352</v>
       </c>
       <c r="B26" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125777424</v>
       </c>
       <c r="B27" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>125777308</v>
       </c>
       <c r="B25" t="n">
-        <v>91922</v>
+        <v>91925</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>125777352</v>
       </c>
       <c r="B26" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125777424</v>
       </c>
       <c r="B27" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>125807652</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>125807658</v>
       </c>
       <c r="B15" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>125807660</v>
       </c>
       <c r="B18" t="n">
-        <v>79054</v>
+        <v>79058</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>125807653</v>
       </c>
       <c r="B19" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>125807656</v>
       </c>
       <c r="B21" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>125807654</v>
       </c>
       <c r="B22" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>125807657</v>
       </c>
       <c r="B23" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>125777308</v>
       </c>
       <c r="B25" t="n">
-        <v>91925</v>
+        <v>91929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>125777352</v>
       </c>
       <c r="B26" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125777424</v>
       </c>
       <c r="B27" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125807653</v>
+        <v>125807659</v>
       </c>
       <c r="B19" t="n">
-        <v>80076</v>
+        <v>75067</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492583</v>
+        <v>492549</v>
       </c>
       <c r="R19" t="n">
-        <v>6939941</v>
+        <v>6939896</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125807659</v>
+        <v>125807653</v>
       </c>
       <c r="B20" t="n">
-        <v>75067</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492549</v>
+        <v>492583</v>
       </c>
       <c r="R20" t="n">
-        <v>6939896</v>
+        <v>6939941</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>125777352</v>
       </c>
       <c r="B26" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125777424</v>
       </c>
       <c r="B27" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>125807652</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>125807651</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>125807658</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>125807660</v>
       </c>
       <c r="B18" t="n">
-        <v>79058</v>
+        <v>79059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125807659</v>
+        <v>125807653</v>
       </c>
       <c r="B19" t="n">
-        <v>75067</v>
+        <v>80077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492549</v>
+        <v>492583</v>
       </c>
       <c r="R19" t="n">
-        <v>6939896</v>
+        <v>6939941</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125807653</v>
+        <v>125807659</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>75068</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492583</v>
+        <v>492549</v>
       </c>
       <c r="R20" t="n">
-        <v>6939941</v>
+        <v>6939896</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2649,7 +2649,7 @@
         <v>125807656</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>125807654</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>125807657</v>
       </c>
       <c r="B23" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>125777308</v>
       </c>
       <c r="B25" t="n">
-        <v>91929</v>
+        <v>91931</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>125777352</v>
       </c>
       <c r="B26" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125777424</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>125777308</v>
       </c>
       <c r="B25" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>125777352</v>
       </c>
       <c r="B26" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125777424</v>
       </c>
       <c r="B27" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125807653</v>
+        <v>125807659</v>
       </c>
       <c r="B19" t="n">
-        <v>80077</v>
+        <v>75068</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492583</v>
+        <v>492549</v>
       </c>
       <c r="R19" t="n">
-        <v>6939941</v>
+        <v>6939896</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125807659</v>
+        <v>125807653</v>
       </c>
       <c r="B20" t="n">
-        <v>75068</v>
+        <v>80077</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492549</v>
+        <v>492583</v>
       </c>
       <c r="R20" t="n">
-        <v>6939896</v>
+        <v>6939941</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>125777308</v>
       </c>
       <c r="B25" t="n">
-        <v>91933</v>
+        <v>91935</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>125777352</v>
       </c>
       <c r="B26" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125777424</v>
       </c>
       <c r="B27" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -3145,7 +3145,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125777352</v>
+        <v>125777424</v>
       </c>
       <c r="B26" t="n">
         <v>98345</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3188,14 +3188,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492414</v>
+        <v>492372</v>
       </c>
       <c r="R26" t="n">
-        <v>6939990</v>
+        <v>6939969</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125777424</v>
+        <v>125777352</v>
       </c>
       <c r="B27" t="n">
         <v>98345</v>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3298,14 +3298,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492372</v>
+        <v>492414</v>
       </c>
       <c r="R27" t="n">
-        <v>6939969</v>
+        <v>6939990</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>125807652</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>125807651</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>125807658</v>
       </c>
       <c r="B15" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>125807660</v>
       </c>
       <c r="B18" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>125807659</v>
       </c>
       <c r="B19" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>125807653</v>
       </c>
       <c r="B20" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>125807656</v>
       </c>
       <c r="B21" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>125807654</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>125807657</v>
       </c>
       <c r="B23" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>125777308</v>
       </c>
       <c r="B25" t="n">
-        <v>91935</v>
+        <v>91939</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>125777424</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125777352</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125807659</v>
+        <v>125807653</v>
       </c>
       <c r="B19" t="n">
-        <v>75072</v>
+        <v>80081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492549</v>
+        <v>492583</v>
       </c>
       <c r="R19" t="n">
-        <v>6939896</v>
+        <v>6939941</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125807653</v>
+        <v>125807659</v>
       </c>
       <c r="B20" t="n">
-        <v>80081</v>
+        <v>75072</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492583</v>
+        <v>492549</v>
       </c>
       <c r="R20" t="n">
-        <v>6939941</v>
+        <v>6939896</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125777424</v>
+        <v>125777352</v>
       </c>
       <c r="B26" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3188,14 +3188,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492372</v>
+        <v>492414</v>
       </c>
       <c r="R26" t="n">
-        <v>6939969</v>
+        <v>6939990</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125777352</v>
+        <v>125777424</v>
       </c>
       <c r="B27" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3298,14 +3298,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492414</v>
+        <v>492372</v>
       </c>
       <c r="R27" t="n">
-        <v>6939990</v>
+        <v>6939969</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125807653</v>
+        <v>125807659</v>
       </c>
       <c r="B19" t="n">
-        <v>80081</v>
+        <v>75072</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492583</v>
+        <v>492549</v>
       </c>
       <c r="R19" t="n">
-        <v>6939941</v>
+        <v>6939896</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125807659</v>
+        <v>125807653</v>
       </c>
       <c r="B20" t="n">
-        <v>75072</v>
+        <v>80081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492549</v>
+        <v>492583</v>
       </c>
       <c r="R20" t="n">
-        <v>6939896</v>
+        <v>6939941</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125807659</v>
+        <v>125807653</v>
       </c>
       <c r="B19" t="n">
-        <v>75072</v>
+        <v>80081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492549</v>
+        <v>492583</v>
       </c>
       <c r="R19" t="n">
-        <v>6939896</v>
+        <v>6939941</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125807653</v>
+        <v>125807659</v>
       </c>
       <c r="B20" t="n">
-        <v>80081</v>
+        <v>75072</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492583</v>
+        <v>492549</v>
       </c>
       <c r="R20" t="n">
-        <v>6939941</v>
+        <v>6939896</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 10873-2024 artfynd.xlsx
+++ b/artfynd/A 10873-2024 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>125807652</v>
       </c>
       <c r="B13" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>125807651</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>125807658</v>
       </c>
       <c r="B15" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>125807666</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125807655</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>125807660</v>
       </c>
       <c r="B18" t="n">
-        <v>79063</v>
+        <v>79066</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>125807653</v>
       </c>
       <c r="B19" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>125807659</v>
       </c>
       <c r="B20" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>125807656</v>
       </c>
       <c r="B21" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>125807654</v>
       </c>
       <c r="B22" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>125807657</v>
       </c>
       <c r="B23" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>125777398</v>
       </c>
       <c r="B24" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>125777308</v>
       </c>
       <c r="B25" t="n">
-        <v>91939</v>
+        <v>91942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>125777352</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125777424</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
